--- a/intermedios/03_enlistamiento/01_concistencia/202412/20242811.xlsx
+++ b/intermedios/03_enlistamiento/01_concistencia/202412/20242811.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="435">
   <si>
     <t xml:space="preserve">pro</t>
   </si>
@@ -90,6 +90,21 @@
     <t xml:space="preserve">t_iden</t>
   </si>
   <si>
+    <t xml:space="preserve">ident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primernjh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segundonjh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primerajh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segudonjh</t>
+  </si>
+  <si>
     <t xml:space="preserve">muje</t>
   </si>
   <si>
@@ -135,9 +150,6 @@
     <t xml:space="preserve">upm</t>
   </si>
   <si>
-    <t xml:space="preserve">primernjh</t>
-  </si>
-  <si>
     <t xml:space="preserve">id_upm</t>
   </si>
   <si>
@@ -171,7 +183,7 @@
     <t xml:space="preserve">009</t>
   </si>
   <si>
-    <t xml:space="preserve">0013</t>
+    <t xml:space="preserve">013</t>
   </si>
   <si>
     <t xml:space="preserve">SANTA TERESITA</t>
@@ -198,7 +210,22 @@
     <t xml:space="preserve">ocupada con personas presentes</t>
   </si>
   <si>
-    <t xml:space="preserve">No Tiene</t>
+    <t xml:space="preserve">Pasaporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0105320410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIINTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULLA</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
@@ -237,22 +264,19 @@
     <t xml:space="preserve">010163900601</t>
   </si>
   <si>
-    <t xml:space="preserve">jose1512</t>
-  </si>
-  <si>
     <t xml:space="preserve">SUR</t>
   </si>
   <si>
     <t xml:space="preserve">010163999009</t>
   </si>
   <si>
-    <t xml:space="preserve">01016399900900100130001</t>
+    <t xml:space="preserve">0101639990090010130001</t>
   </si>
   <si>
     <t xml:space="preserve">021</t>
   </si>
   <si>
-    <t xml:space="preserve">0038</t>
+    <t xml:space="preserve">038</t>
   </si>
   <si>
     <t xml:space="preserve">LLIGUIÑA</t>
@@ -261,6 +285,24 @@
     <t xml:space="preserve">CARRETERO A SHIHUIN</t>
   </si>
   <si>
+    <t xml:space="preserve">Cédula de Identidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0102943297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOJANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOROCHO</t>
+  </si>
+  <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
@@ -279,13 +321,10 @@
     <t xml:space="preserve">010163901101</t>
   </si>
   <si>
-    <t xml:space="preserve">jose1865</t>
-  </si>
-  <si>
     <t xml:space="preserve">010163999021</t>
   </si>
   <si>
-    <t xml:space="preserve">01016399902100100380001</t>
+    <t xml:space="preserve">0101639990210010380001</t>
   </si>
   <si>
     <t xml:space="preserve">04</t>
@@ -303,9 +342,6 @@
     <t xml:space="preserve">002</t>
   </si>
   <si>
-    <t xml:space="preserve">0009</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pasaje</t>
   </si>
   <si>
@@ -327,6 +363,18 @@
     <t xml:space="preserve">1-3</t>
   </si>
   <si>
+    <t xml:space="preserve">0400896296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPINOSA</t>
+  </si>
+  <si>
     <t xml:space="preserve">0967817731</t>
   </si>
   <si>
@@ -342,16 +390,13 @@
     <t xml:space="preserve">040252000501</t>
   </si>
   <si>
-    <t xml:space="preserve">jose6554</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADM. C. CAMPO</t>
   </si>
   <si>
     <t xml:space="preserve">040252908002001</t>
   </si>
   <si>
-    <t xml:space="preserve">04025290800200100090001</t>
+    <t xml:space="preserve">0402529080020010090001</t>
   </si>
   <si>
     <t xml:space="preserve">03</t>
@@ -363,7 +408,7 @@
     <t xml:space="preserve">006</t>
   </si>
   <si>
-    <t xml:space="preserve">0114</t>
+    <t xml:space="preserve">114</t>
   </si>
   <si>
     <t xml:space="preserve">SAN JOSE DE CHABAYAN</t>
@@ -375,6 +420,21 @@
     <t xml:space="preserve">VIA ASFALTADA SAN JOSE DE CHABAYAN</t>
   </si>
   <si>
+    <t xml:space="preserve">Cédula de otro miembro del hogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIMENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUASCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASPUEZAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">INFORMACION DADA POR VECINA</t>
   </si>
   <si>
@@ -390,13 +450,22 @@
     <t xml:space="preserve">040350900301</t>
   </si>
   <si>
-    <t xml:space="preserve">jose6668</t>
-  </si>
-  <si>
     <t xml:space="preserve">040350999006</t>
   </si>
   <si>
-    <t xml:space="preserve">04035099900600101140001</t>
+    <t xml:space="preserve">0403509990060011140001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0400567996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MITES</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -414,13 +483,10 @@
     <t xml:space="preserve">2024-11-12 02:58:18.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose6669</t>
-  </si>
-  <si>
     <t xml:space="preserve">07</t>
   </si>
   <si>
-    <t xml:space="preserve">0015</t>
+    <t xml:space="preserve">015</t>
   </si>
   <si>
     <t xml:space="preserve">W</t>
@@ -432,6 +498,18 @@
     <t xml:space="preserve">17-B</t>
   </si>
   <si>
+    <t xml:space="preserve">0703095745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELCISNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTANO</t>
+  </si>
+  <si>
     <t xml:space="preserve">22</t>
   </si>
   <si>
@@ -450,13 +528,10 @@
     <t xml:space="preserve">070150010701</t>
   </si>
   <si>
-    <t xml:space="preserve">jose10314</t>
-  </si>
-  <si>
     <t xml:space="preserve">070150021006006</t>
   </si>
   <si>
-    <t xml:space="preserve">07015002100600600150001</t>
+    <t xml:space="preserve">0701500210060060150001</t>
   </si>
   <si>
     <t xml:space="preserve">08</t>
@@ -468,7 +543,7 @@
     <t xml:space="preserve">005</t>
   </si>
   <si>
-    <t xml:space="preserve">0063</t>
+    <t xml:space="preserve">063</t>
   </si>
   <si>
     <t xml:space="preserve">AUGUSTO POLANCO</t>
@@ -480,6 +555,18 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
+    <t xml:space="preserve">0801640806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELOCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAUTISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TENORIO</t>
+  </si>
+  <si>
     <t xml:space="preserve">0984243081</t>
   </si>
   <si>
@@ -492,13 +579,10 @@
     <t xml:space="preserve">080150025901</t>
   </si>
   <si>
-    <t xml:space="preserve">jose12676</t>
-  </si>
-  <si>
     <t xml:space="preserve">080150016005001</t>
   </si>
   <si>
-    <t xml:space="preserve">08015001600500100630001</t>
+    <t xml:space="preserve">0801500160050010630001</t>
   </si>
   <si>
     <t xml:space="preserve">09</t>
@@ -507,7 +591,7 @@
     <t xml:space="preserve">499</t>
   </si>
   <si>
-    <t xml:space="preserve">0024</t>
+    <t xml:space="preserve">024</t>
   </si>
   <si>
     <t xml:space="preserve">3RA PEAT. 38C N-O</t>
@@ -519,6 +603,24 @@
     <t xml:space="preserve">0002</t>
   </si>
   <si>
+    <t xml:space="preserve">Otro documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21407947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAZQUEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
@@ -534,16 +636,13 @@
     <t xml:space="preserve">090150157301</t>
   </si>
   <si>
-    <t xml:space="preserve">jose16054</t>
-  </si>
-  <si>
     <t xml:space="preserve">LITORAL</t>
   </si>
   <si>
     <t xml:space="preserve">090150499006001</t>
   </si>
   <si>
-    <t xml:space="preserve">09015049900600100240002</t>
+    <t xml:space="preserve">0901504990060010240002</t>
   </si>
   <si>
     <t xml:space="preserve">521</t>
@@ -558,6 +657,18 @@
     <t xml:space="preserve">Y</t>
   </si>
   <si>
+    <t xml:space="preserve">0602353047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHIMBOLEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUJILEMA</t>
+  </si>
+  <si>
     <t xml:space="preserve">SON 2 HOGARES</t>
   </si>
   <si>
@@ -573,16 +684,13 @@
     <t xml:space="preserve">090150277101</t>
   </si>
   <si>
-    <t xml:space="preserve">jose16105</t>
-  </si>
-  <si>
     <t xml:space="preserve">090150521004001</t>
   </si>
   <si>
-    <t xml:space="preserve">09015052100400100240001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0003</t>
+    <t xml:space="preserve">0901505210040010240001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">003</t>
   </si>
   <si>
     <t xml:space="preserve">18A</t>
@@ -591,6 +699,21 @@
     <t xml:space="preserve">X</t>
   </si>
   <si>
+    <t xml:space="preserve">0908275035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAGUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELTRAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
@@ -600,19 +723,16 @@
     <t xml:space="preserve">2024-11-15 08:57:53.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose16186</t>
-  </si>
-  <si>
     <t xml:space="preserve">090150521005002</t>
   </si>
   <si>
-    <t xml:space="preserve">09015052100500200030001</t>
+    <t xml:space="preserve">0901505210050020030001</t>
   </si>
   <si>
     <t xml:space="preserve">528</t>
   </si>
   <si>
-    <t xml:space="preserve">0029</t>
+    <t xml:space="preserve">029</t>
   </si>
   <si>
     <t xml:space="preserve">72</t>
@@ -621,6 +741,21 @@
     <t xml:space="preserve">R</t>
   </si>
   <si>
+    <t xml:space="preserve">0914971080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAVIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAJARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREVALO</t>
+  </si>
+  <si>
     <t xml:space="preserve">0990098851</t>
   </si>
   <si>
@@ -630,13 +765,10 @@
     <t xml:space="preserve">090150282201</t>
   </si>
   <si>
-    <t xml:space="preserve">jose16254</t>
-  </si>
-  <si>
     <t xml:space="preserve">090150528001002</t>
   </si>
   <si>
-    <t xml:space="preserve">09015052800100200290001</t>
+    <t xml:space="preserve">0901505280010020290001</t>
   </si>
   <si>
     <t xml:space="preserve">593</t>
@@ -645,7 +777,7 @@
     <t xml:space="preserve">011</t>
   </si>
   <si>
-    <t xml:space="preserve">0007</t>
+    <t xml:space="preserve">007</t>
   </si>
   <si>
     <t xml:space="preserve">44</t>
@@ -654,6 +786,21 @@
     <t xml:space="preserve">F-1</t>
   </si>
   <si>
+    <t xml:space="preserve">1301268049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELICICIMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTOBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLUAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINO</t>
+  </si>
+  <si>
     <t xml:space="preserve">0983079097</t>
   </si>
   <si>
@@ -666,13 +813,10 @@
     <t xml:space="preserve">090150170401</t>
   </si>
   <si>
-    <t xml:space="preserve">jose16471</t>
-  </si>
-  <si>
     <t xml:space="preserve">090150593011005</t>
   </si>
   <si>
-    <t xml:space="preserve">09015059301100500070001</t>
+    <t xml:space="preserve">0901505930110050070001</t>
   </si>
   <si>
     <t xml:space="preserve">10</t>
@@ -687,6 +831,18 @@
     <t xml:space="preserve">JUAN OCLES</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELADIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINA</t>
+  </si>
+  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
@@ -702,13 +858,10 @@
     <t xml:space="preserve">100151000901</t>
   </si>
   <si>
-    <t xml:space="preserve">jose18298</t>
-  </si>
-  <si>
     <t xml:space="preserve">100151907002002</t>
   </si>
   <si>
-    <t xml:space="preserve">10015190700200200090002</t>
+    <t xml:space="preserve">1001519070020020090002</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
@@ -720,18 +873,27 @@
     <t xml:space="preserve">53</t>
   </si>
   <si>
-    <t xml:space="preserve">013</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA SUCRE</t>
   </si>
   <si>
-    <t xml:space="preserve">003</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARRETERA LASTRADA  LA SUCRE A  LAS PALMAS</t>
   </si>
   <si>
+    <t xml:space="preserve">1208230811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVILES</t>
+  </si>
+  <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
@@ -744,13 +906,10 @@
     <t xml:space="preserve">120553901101</t>
   </si>
   <si>
-    <t xml:space="preserve">jose22653</t>
-  </si>
-  <si>
     <t xml:space="preserve">120553999013</t>
   </si>
   <si>
-    <t xml:space="preserve">12055399901300301140001</t>
+    <t xml:space="preserve">1205539990130031140001</t>
   </si>
   <si>
     <t xml:space="preserve">13</t>
@@ -759,7 +918,7 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
-    <t xml:space="preserve">0012</t>
+    <t xml:space="preserve">012</t>
   </si>
   <si>
     <t xml:space="preserve">ELOY ALFARO DELGAD</t>
@@ -768,6 +927,21 @@
     <t xml:space="preserve">A - 1</t>
   </si>
   <si>
+    <t xml:space="preserve">1307249738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARGARITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEBALLOS</t>
+  </si>
+  <si>
     <t xml:space="preserve">0982702241</t>
   </si>
   <si>
@@ -780,24 +954,33 @@
     <t xml:space="preserve">131550000501</t>
   </si>
   <si>
-    <t xml:space="preserve">jose26036</t>
-  </si>
-  <si>
     <t xml:space="preserve">131550001004003</t>
   </si>
   <si>
-    <t xml:space="preserve">13155000100400300120001</t>
+    <t xml:space="preserve">1315500010040030120001</t>
   </si>
   <si>
     <t xml:space="preserve">16</t>
   </si>
   <si>
-    <t xml:space="preserve">012</t>
-  </si>
-  <si>
     <t xml:space="preserve">JAIME ROLDOS AGUILERA</t>
   </si>
   <si>
+    <t xml:space="preserve">1600400137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONIZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">0989593397</t>
   </si>
   <si>
@@ -810,16 +993,13 @@
     <t xml:space="preserve">160350000501</t>
   </si>
   <si>
-    <t xml:space="preserve">jose30092</t>
-  </si>
-  <si>
     <t xml:space="preserve">CENTRO</t>
   </si>
   <si>
     <t xml:space="preserve">160350001003012</t>
   </si>
   <si>
-    <t xml:space="preserve">16035000100301200030001</t>
+    <t xml:space="preserve">1603500010030120030001</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
@@ -831,7 +1011,7 @@
     <t xml:space="preserve">025</t>
   </si>
   <si>
-    <t xml:space="preserve">0042</t>
+    <t xml:space="preserve">042</t>
   </si>
   <si>
     <t xml:space="preserve">BELLAVISTA</t>
@@ -843,6 +1023,21 @@
     <t xml:space="preserve">ASFALTADO</t>
   </si>
   <si>
+    <t xml:space="preserve">1802893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CECILIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAMAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUEVARA</t>
+  </si>
+  <si>
     <t xml:space="preserve">0996110570</t>
   </si>
   <si>
@@ -852,19 +1047,16 @@
     <t xml:space="preserve">180165901201</t>
   </si>
   <si>
-    <t xml:space="preserve">jose35122</t>
-  </si>
-  <si>
     <t xml:space="preserve">180165999025</t>
   </si>
   <si>
-    <t xml:space="preserve">18016599902500100420001</t>
+    <t xml:space="preserve">1801659990250010420001</t>
   </si>
   <si>
     <t xml:space="preserve">59</t>
   </si>
   <si>
-    <t xml:space="preserve">0055</t>
+    <t xml:space="preserve">055</t>
   </si>
   <si>
     <t xml:space="preserve">SAN LORENZO</t>
@@ -873,6 +1065,21 @@
     <t xml:space="preserve">LASTRADO</t>
   </si>
   <si>
+    <t xml:space="preserve">1500624828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANGUILA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREFA</t>
+  </si>
+  <si>
     <t xml:space="preserve">0999116700</t>
   </si>
   <si>
@@ -885,13 +1092,10 @@
     <t xml:space="preserve">220159900101</t>
   </si>
   <si>
-    <t xml:space="preserve">jose40616</t>
-  </si>
-  <si>
     <t xml:space="preserve">220159999002</t>
   </si>
   <si>
-    <t xml:space="preserve">22015999900200100550001</t>
+    <t xml:space="preserve">2201599990020010550001</t>
   </si>
   <si>
     <t xml:space="preserve">24</t>
@@ -900,7 +1104,19 @@
     <t xml:space="preserve">940</t>
   </si>
   <si>
-    <t xml:space="preserve">015</t>
+    <t xml:space="preserve">0915774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORENCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGALLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMALA</t>
   </si>
   <si>
     <t xml:space="preserve">0980721021</t>
@@ -915,21 +1131,30 @@
     <t xml:space="preserve">240152003301</t>
   </si>
   <si>
-    <t xml:space="preserve">jose42925</t>
-  </si>
-  <si>
     <t xml:space="preserve">240152940002015</t>
   </si>
   <si>
-    <t xml:space="preserve">24015294000201500070001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007</t>
+    <t xml:space="preserve">2401529400020150070001</t>
   </si>
   <si>
     <t xml:space="preserve">008</t>
   </si>
   <si>
+    <t xml:space="preserve">0920855798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENRIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORONADO</t>
+  </si>
+  <si>
     <t xml:space="preserve">0990048301</t>
   </si>
   <si>
@@ -942,16 +1167,25 @@
     <t xml:space="preserve">240350006601</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43144</t>
-  </si>
-  <si>
     <t xml:space="preserve">240350007008004</t>
   </si>
   <si>
-    <t xml:space="preserve">24035000700800400030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0004</t>
+    <t xml:space="preserve">2403500070080040030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0924688047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGRID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOHANNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHELE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIGRERO</t>
   </si>
   <si>
     <t xml:space="preserve">0979834319</t>
@@ -963,18 +1197,24 @@
     <t xml:space="preserve">2024-11-10 12:48:15.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24035000700800400040001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0014</t>
+    <t xml:space="preserve">2403500070080040040001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">014</t>
   </si>
   <si>
     <t xml:space="preserve">PLAYAS</t>
   </si>
   <si>
+    <t xml:space="preserve">0928144765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDALENA</t>
+  </si>
+  <si>
     <t xml:space="preserve">0991584490</t>
   </si>
   <si>
@@ -984,31 +1224,49 @@
     <t xml:space="preserve">2024-11-10 08:29:26.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24035000700800400140001</t>
+    <t xml:space="preserve">2403500070080040140001</t>
   </si>
   <si>
     <t xml:space="preserve">JULIO JARAMILLO</t>
   </si>
   <si>
+    <t xml:space="preserve">0917406217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAINEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">0980947822</t>
   </si>
   <si>
     <t xml:space="preserve">2024-11-09 07:01:59.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43191</t>
-  </si>
-  <si>
     <t xml:space="preserve">240350007009006</t>
   </si>
   <si>
-    <t xml:space="preserve">24035000700900600040001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0011</t>
+    <t xml:space="preserve">2403500070090060040001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0912157831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HILDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZUCENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEJILLON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGEL</t>
   </si>
   <si>
     <t xml:space="preserve">0987599509</t>
@@ -1020,10 +1278,19 @@
     <t xml:space="preserve">2024-11-10 09:46:01.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24035000700900600110001</t>
+    <t xml:space="preserve">2403500070090060110001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2400250193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCKLIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEREJILDO</t>
   </si>
   <si>
     <t xml:space="preserve">0985566402</t>
@@ -1035,10 +1302,7 @@
     <t xml:space="preserve">2024-11-09 08:26:02.0</t>
   </si>
   <si>
-    <t xml:space="preserve">jose43207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24035000700900600130001</t>
+    <t xml:space="preserve">2403500070090060130001</t>
   </si>
   <si>
     <t xml:space="preserve">viv_act</t>
@@ -1527,41 +1791,53 @@
       <c r="AV1" t="s">
         <v>47</v>
       </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2"/>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M2"/>
       <c r="N2"/>
@@ -1569,121 +1845,133 @@
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S2"/>
       <c r="T2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V2"/>
       <c r="W2"/>
       <c r="X2"/>
       <c r="Y2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AA2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB2" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG2" t="n">
         <v>14</v>
       </c>
-      <c r="AC2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD2"/>
-      <c r="AE2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>67</v>
-      </c>
       <c r="AH2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>69</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="AI2"/>
       <c r="AJ2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK2"/>
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>75</v>
+      </c>
       <c r="AL2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AM2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AO2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>73</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP2"/>
       <c r="AQ2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AS2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="AT2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F3"/>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="M3"/>
       <c r="N3"/>
@@ -1691,247 +1979,269 @@
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V3"/>
       <c r="W3"/>
       <c r="X3"/>
       <c r="Y3" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AA3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB3" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG3" t="n">
         <v>13</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AH3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3"/>
+      <c r="AJ3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP3"/>
+      <c r="AQ3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU3" t="s">
         <v>83</v>
       </c>
-      <c r="AD3"/>
-      <c r="AE3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK3"/>
-      <c r="AL3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY3" t="n">
         <v>0</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="O4" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q4"/>
       <c r="R4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="S4"/>
       <c r="T4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V4"/>
       <c r="W4"/>
       <c r="X4"/>
       <c r="Y4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AA4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB4" t="n">
+        <v>117</v>
+      </c>
+      <c r="AB4"/>
+      <c r="AC4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG4" t="n">
         <v>13</v>
       </c>
-      <c r="AC4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD4"/>
-      <c r="AE4" t="s">
-        <v>105</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>67</v>
-      </c>
       <c r="AH4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>69</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="AI4"/>
       <c r="AJ4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK4"/>
+        <v>121</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>122</v>
+      </c>
       <c r="AL4" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AM4" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN4" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AO4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>108</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP4"/>
       <c r="AQ4" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="AR4" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="AS4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="AT4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AU4" t="n">
+        <v>124</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY4" t="n">
         <v>0</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K5" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="M5"/>
       <c r="N5"/>
@@ -1939,121 +2249,131 @@
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S5"/>
       <c r="T5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V5"/>
       <c r="W5"/>
       <c r="X5"/>
       <c r="Y5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>55</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="Z5"/>
       <c r="AA5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB5" t="n">
+        <v>136</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG5" t="n">
         <v>4</v>
       </c>
-      <c r="AC5"/>
-      <c r="AD5"/>
-      <c r="AE5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>69</v>
-      </c>
+      <c r="AH5"/>
+      <c r="AI5"/>
       <c r="AJ5" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="s">
         <v>122</v>
       </c>
       <c r="AL5" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="AM5" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN5" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AO5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU5" t="s">
         <v>125</v>
       </c>
-      <c r="AP5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>126</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>127</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L6" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
@@ -2061,1125 +2381,1229 @@
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S6"/>
       <c r="T6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V6"/>
       <c r="W6"/>
       <c r="X6"/>
       <c r="Y6" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z6" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="AA6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AG6" t="n">
         <v>5</v>
       </c>
-      <c r="AC6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE6"/>
-      <c r="AF6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>67</v>
-      </c>
       <c r="AH6" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="AI6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>121</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="AJ6"/>
       <c r="AK6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AL6" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AM6" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN6" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AO6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AP6" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="AQ6" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="AR6" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="AS6" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="AT6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AU6" t="n">
+        <v>144</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="M7" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="N7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q7"/>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S7"/>
       <c r="T7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V7"/>
       <c r="W7"/>
       <c r="X7"/>
       <c r="Y7" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z7" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="AA7" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB7" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG7" t="n">
         <v>33</v>
       </c>
-      <c r="AC7" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD7"/>
-      <c r="AE7"/>
-      <c r="AF7" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>67</v>
-      </c>
       <c r="AH7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK7"/>
+        <v>167</v>
+      </c>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7" t="s">
+        <v>168</v>
+      </c>
       <c r="AL7" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="AM7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN7" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="AO7" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>144</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP7"/>
       <c r="AQ7" t="s">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="AR7" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="AS7" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="AT7" t="s">
-        <v>147</v>
-      </c>
-      <c r="AU7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>172</v>
+      </c>
+      <c r="AY7" t="n">
         <v>0</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="M8" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="N8" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="O8" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q8"/>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S8"/>
       <c r="T8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V8"/>
       <c r="W8"/>
       <c r="X8"/>
       <c r="Y8" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z8" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="AA8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB8" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG8" t="n">
         <v>15</v>
       </c>
-      <c r="AC8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD8"/>
-      <c r="AE8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>67</v>
-      </c>
       <c r="AH8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>69</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AI8"/>
       <c r="AJ8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK8"/>
+        <v>185</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>168</v>
+      </c>
       <c r="AL8" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="AM8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN8" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="AO8" t="s">
-        <v>159</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>158</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP8"/>
       <c r="AQ8" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="AR8" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="AS8" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AT8" t="s">
-        <v>161</v>
-      </c>
-      <c r="AU8" t="n">
+        <v>187</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>188</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>189</v>
+      </c>
+      <c r="AY8" t="n">
         <v>0</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="L9" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="M9" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="N9" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="O9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q9"/>
       <c r="R9" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="S9"/>
       <c r="T9" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="U9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V9"/>
       <c r="W9"/>
       <c r="X9"/>
       <c r="Y9" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="Z9" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI9"/>
+      <c r="AJ9" t="s">
+        <v>204</v>
+      </c>
+      <c r="AK9" t="s">
         <v>168</v>
       </c>
-      <c r="AA9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD9"/>
-      <c r="AE9" t="s">
-        <v>170</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK9"/>
       <c r="AL9" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN9" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AO9" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>172</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP9"/>
       <c r="AQ9" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="AR9" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="AS9" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="AT9" t="s">
-        <v>176</v>
-      </c>
-      <c r="AU9" t="n">
+        <v>206</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>208</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>209</v>
+      </c>
+      <c r="AY9" t="n">
         <v>0</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L10" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N10" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q10"/>
       <c r="R10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S10"/>
       <c r="T10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V10"/>
       <c r="W10"/>
       <c r="X10"/>
       <c r="Y10" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z10" t="s">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="AA10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB10" t="n">
+        <v>215</v>
+      </c>
+      <c r="AB10"/>
+      <c r="AC10" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG10" t="n">
         <v>15</v>
       </c>
-      <c r="AC10"/>
-      <c r="AD10"/>
-      <c r="AE10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>69</v>
-      </c>
+      <c r="AH10"/>
+      <c r="AI10"/>
       <c r="AJ10" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="AK10" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AL10" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN10" t="s">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AO10" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="AP10" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="AQ10" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="AR10" t="s">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="AS10" t="s">
-        <v>54</v>
+        <v>222</v>
       </c>
       <c r="AT10" t="s">
-        <v>188</v>
-      </c>
-      <c r="AU10" t="n">
+        <v>222</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>223</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>224</v>
+      </c>
+      <c r="AY10" t="n">
         <v>0</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N11" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="O11" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q11"/>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S11"/>
       <c r="T11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V11"/>
       <c r="W11"/>
       <c r="X11"/>
       <c r="Y11" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z11" t="s">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="AA11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB11" t="n">
+        <v>229</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG11" t="n">
         <v>13</v>
       </c>
-      <c r="AC11"/>
-      <c r="AD11"/>
-      <c r="AE11" t="s">
-        <v>193</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>69</v>
-      </c>
+      <c r="AH11"/>
+      <c r="AI11"/>
       <c r="AJ11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK11"/>
+        <v>234</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>122</v>
+      </c>
       <c r="AL11" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="AM11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN11" t="s">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AO11" t="s">
-        <v>195</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>185</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP11"/>
       <c r="AQ11" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="AR11" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AS11" t="s">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="AT11" t="s">
-        <v>197</v>
-      </c>
-      <c r="AU11" t="n">
+        <v>222</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>236</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>237</v>
+      </c>
+      <c r="AY11" t="n">
         <v>0</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="M12" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N12" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="O12" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S12"/>
       <c r="T12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V12"/>
       <c r="W12"/>
       <c r="X12"/>
       <c r="Y12" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z12" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="AA12" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB12" t="n">
+        <v>243</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>244</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>246</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG12" t="n">
         <v>14</v>
       </c>
-      <c r="AC12" t="s">
-        <v>202</v>
-      </c>
-      <c r="AD12"/>
-      <c r="AE12"/>
-      <c r="AF12" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>67</v>
-      </c>
       <c r="AH12" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK12"/>
+        <v>247</v>
+      </c>
+      <c r="AI12"/>
+      <c r="AJ12"/>
+      <c r="AK12" t="s">
+        <v>168</v>
+      </c>
       <c r="AL12" t="s">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="AM12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AO12" t="s">
-        <v>205</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>204</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP12"/>
       <c r="AQ12" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="AR12" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AS12" t="s">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="AT12" t="s">
+        <v>249</v>
+      </c>
+      <c r="AU12" t="s">
         <v>207</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="s">
+        <v>250</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>251</v>
+      </c>
+      <c r="AY12" t="n">
         <v>0</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="F13" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N13" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q13"/>
       <c r="R13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S13"/>
       <c r="T13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V13"/>
       <c r="W13"/>
       <c r="X13"/>
       <c r="Y13" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z13" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>260</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>262</v>
+      </c>
+      <c r="AI13"/>
+      <c r="AJ13" t="s">
+        <v>263</v>
+      </c>
+      <c r="AK13" t="s">
         <v>168</v>
       </c>
-      <c r="AA13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD13"/>
-      <c r="AE13" t="s">
-        <v>214</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK13"/>
       <c r="AL13" t="s">
-        <v>215</v>
+        <v>76</v>
       </c>
       <c r="AM13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="AO13" t="s">
-        <v>217</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>216</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP13"/>
       <c r="AQ13" t="s">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="AR13" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="AS13" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="AT13" t="s">
-        <v>219</v>
-      </c>
-      <c r="AU13" t="n">
+        <v>265</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>267</v>
+      </c>
+      <c r="AY13" t="n">
         <v>0</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AZ13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P14" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q14"/>
       <c r="R14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S14"/>
       <c r="T14" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="U14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
       <c r="Y14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>168</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="Z14"/>
       <c r="AA14" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB14" t="n">
+        <v>272</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>275</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG14" t="n">
         <v>22</v>
       </c>
-      <c r="AC14" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD14"/>
-      <c r="AE14" t="s">
-        <v>226</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>67</v>
-      </c>
       <c r="AH14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>69</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="AI14"/>
       <c r="AJ14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK14"/>
+        <v>278</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>75</v>
+      </c>
       <c r="AL14" t="s">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="AM14" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN14" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AO14" t="s">
-        <v>229</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>228</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP14"/>
       <c r="AQ14" t="s">
-        <v>110</v>
+        <v>279</v>
       </c>
       <c r="AR14" t="s">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AS14" t="s">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="AT14" t="s">
-        <v>231</v>
-      </c>
-      <c r="AU14" t="n">
+        <v>280</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>281</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>282</v>
+      </c>
+      <c r="AY14" t="n">
         <v>0</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AZ14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="F15"/>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H15" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="I15" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="J15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L15" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="M15"/>
       <c r="N15"/>
@@ -3187,1468 +3611,1612 @@
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S15"/>
       <c r="T15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V15"/>
       <c r="W15"/>
       <c r="X15"/>
       <c r="Y15" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z15" t="s">
-        <v>239</v>
+        <v>288</v>
       </c>
       <c r="AA15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AB15" t="n">
+        <v>289</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>290</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>292</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG15" t="n">
         <v>24</v>
       </c>
-      <c r="AC15" t="s">
-        <v>240</v>
-      </c>
-      <c r="AD15"/>
-      <c r="AE15"/>
-      <c r="AF15" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>67</v>
-      </c>
       <c r="AH15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK15"/>
+        <v>294</v>
+      </c>
+      <c r="AI15"/>
+      <c r="AJ15"/>
+      <c r="AK15" t="s">
+        <v>75</v>
+      </c>
       <c r="AL15" t="s">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AM15" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN15" t="s">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AO15" t="s">
-        <v>243</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>242</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP15"/>
       <c r="AQ15" t="s">
-        <v>174</v>
+        <v>295</v>
       </c>
       <c r="AR15" t="s">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AS15" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="AT15" t="s">
-        <v>245</v>
-      </c>
-      <c r="AU15" t="n">
+        <v>296</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>297</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>225</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>298</v>
+      </c>
+      <c r="AY15" t="n">
         <v>0</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AZ15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="F16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G16" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="M16" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N16" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
       <c r="O16" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q16"/>
       <c r="R16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S16"/>
       <c r="T16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V16"/>
       <c r="W16"/>
       <c r="X16"/>
       <c r="Y16" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z16" t="s">
-        <v>168</v>
+        <v>304</v>
       </c>
       <c r="AA16" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB16" t="n">
+        <v>305</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>308</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG16" t="n">
         <v>13</v>
       </c>
-      <c r="AC16" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD16"/>
-      <c r="AE16" t="s">
-        <v>252</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>67</v>
-      </c>
       <c r="AH16" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>69</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="AI16"/>
       <c r="AJ16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK16"/>
+        <v>310</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>122</v>
+      </c>
       <c r="AL16" t="s">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="AM16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AO16" t="s">
-        <v>255</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>254</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP16"/>
       <c r="AQ16" t="s">
-        <v>174</v>
+        <v>311</v>
       </c>
       <c r="AR16" t="s">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AS16" t="s">
-        <v>237</v>
+        <v>312</v>
       </c>
       <c r="AT16" t="s">
-        <v>257</v>
-      </c>
-      <c r="AU16" t="n">
+        <v>312</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>313</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>314</v>
+      </c>
+      <c r="AY16" t="n">
         <v>0</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AZ16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N17" t="s">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="O17" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P17" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q17"/>
       <c r="R17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S17"/>
       <c r="T17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V17"/>
       <c r="W17"/>
       <c r="X17"/>
       <c r="Y17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z17" t="s">
-        <v>62</v>
+        <v>317</v>
       </c>
       <c r="AA17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="n">
+        <v>318</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>319</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>321</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG17" t="n">
         <v>15</v>
       </c>
-      <c r="AC17" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD17"/>
-      <c r="AE17" t="s">
-        <v>262</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>67</v>
-      </c>
       <c r="AH17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>69</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="AI17"/>
       <c r="AJ17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK17"/>
+        <v>323</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>75</v>
+      </c>
       <c r="AL17" t="s">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="AM17" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN17" t="s">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="AO17" t="s">
-        <v>265</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>264</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP17"/>
       <c r="AQ17" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="AR17" t="s">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AS17" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="AT17" t="s">
-        <v>268</v>
-      </c>
-      <c r="AU17" t="n">
+        <v>325</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>326</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>327</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>301</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>328</v>
+      </c>
+      <c r="AY17" t="n">
         <v>0</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AZ17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>271</v>
+        <v>331</v>
       </c>
       <c r="F18"/>
       <c r="G18" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="H18" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="I18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="M18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="O18"/>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S18"/>
       <c r="T18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V18"/>
       <c r="W18"/>
       <c r="X18"/>
       <c r="Y18" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z18" t="s">
-        <v>98</v>
+        <v>336</v>
       </c>
       <c r="AA18" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB18" t="n">
+        <v>337</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>338</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG18" t="n">
         <v>14</v>
       </c>
-      <c r="AC18" t="s">
-        <v>276</v>
-      </c>
-      <c r="AD18"/>
-      <c r="AE18"/>
-      <c r="AF18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>67</v>
-      </c>
       <c r="AH18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK18"/>
+        <v>341</v>
+      </c>
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18" t="s">
+        <v>75</v>
+      </c>
       <c r="AL18" t="s">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AM18" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN18" t="s">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="AO18" t="s">
-        <v>279</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>278</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP18"/>
       <c r="AQ18" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="AR18" t="s">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="AS18" t="s">
-        <v>54</v>
+        <v>343</v>
       </c>
       <c r="AT18" t="s">
-        <v>281</v>
-      </c>
-      <c r="AU18" t="n">
+        <v>343</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>326</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>344</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>345</v>
+      </c>
+      <c r="AY18" t="n">
         <v>0</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AZ18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F19"/>
       <c r="G19" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="H19" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="I19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K19" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="M19" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="N19" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="O19"/>
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S19"/>
       <c r="T19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V19"/>
       <c r="W19"/>
       <c r="X19"/>
       <c r="Y19" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z19" t="s">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AA19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB19" t="n">
+        <v>351</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>352</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>353</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG19" t="n">
         <v>13</v>
       </c>
-      <c r="AC19" t="s">
-        <v>286</v>
-      </c>
-      <c r="AD19"/>
-      <c r="AE19" t="s">
-        <v>287</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>67</v>
-      </c>
       <c r="AH19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>69</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="AI19"/>
       <c r="AJ19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK19"/>
+        <v>356</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>75</v>
+      </c>
       <c r="AL19" t="s">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="AM19" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AN19" t="s">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s">
-        <v>290</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>289</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP19"/>
       <c r="AQ19" t="s">
-        <v>266</v>
+        <v>357</v>
       </c>
       <c r="AR19" t="s">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="AS19" t="s">
-        <v>54</v>
+        <v>358</v>
       </c>
       <c r="AT19" t="s">
-        <v>292</v>
-      </c>
-      <c r="AU19" t="n">
+        <v>358</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>326</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>359</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>360</v>
+      </c>
+      <c r="AY19" t="n">
         <v>0</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AZ19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N20" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O20" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P20" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q20"/>
       <c r="R20" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S20"/>
       <c r="T20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V20"/>
       <c r="W20"/>
       <c r="X20"/>
       <c r="Y20" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z20" t="s">
-        <v>220</v>
+        <v>363</v>
       </c>
       <c r="AA20" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB20" t="n">
+        <v>364</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>366</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG20" t="n">
         <v>14</v>
       </c>
-      <c r="AC20" t="s">
-        <v>296</v>
-      </c>
-      <c r="AD20"/>
-      <c r="AE20" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>67</v>
-      </c>
       <c r="AH20" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>69</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="AI20"/>
       <c r="AJ20" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="AK20" t="s">
-        <v>297</v>
+        <v>122</v>
       </c>
       <c r="AL20" t="s">
-        <v>298</v>
+        <v>76</v>
       </c>
       <c r="AM20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="AO20" t="s">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AP20" t="s">
-        <v>299</v>
+        <v>369</v>
       </c>
       <c r="AQ20" t="s">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="AR20" t="s">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="AS20" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="AT20" t="s">
-        <v>302</v>
-      </c>
-      <c r="AU20" t="n">
+        <v>371</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>372</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>157</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>373</v>
+      </c>
+      <c r="AY20" t="n">
         <v>0</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AZ20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="F21" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="G21" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N21" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O21" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P21" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q21"/>
       <c r="R21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S21"/>
       <c r="T21" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="U21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V21"/>
       <c r="W21"/>
       <c r="X21"/>
       <c r="Y21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z21" t="s">
-        <v>140</v>
+        <v>375</v>
       </c>
       <c r="AA21" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB21" t="n">
+        <v>376</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>377</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>378</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>379</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG21" t="n">
         <v>18</v>
       </c>
-      <c r="AC21" t="s">
-        <v>305</v>
-      </c>
-      <c r="AD21"/>
-      <c r="AE21" t="s">
-        <v>306</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>67</v>
-      </c>
       <c r="AH21" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>69</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AI21"/>
       <c r="AJ21" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK21"/>
+        <v>381</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>122</v>
+      </c>
       <c r="AL21" t="s">
-        <v>307</v>
+        <v>76</v>
       </c>
       <c r="AM21" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s">
-        <v>309</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP21"/>
       <c r="AQ21" t="s">
-        <v>174</v>
+        <v>382</v>
       </c>
       <c r="AR21" t="s">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AS21" t="s">
-        <v>178</v>
+        <v>383</v>
       </c>
       <c r="AT21" t="s">
-        <v>311</v>
-      </c>
-      <c r="AU21" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>384</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>385</v>
+      </c>
+      <c r="AY21" t="n">
         <v>0</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AZ21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E22" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="F22" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="G22" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N22" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O22" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P22" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q22"/>
       <c r="R22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S22"/>
       <c r="T22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22"/>
       <c r="Y22" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z22" t="s">
-        <v>220</v>
+        <v>386</v>
       </c>
       <c r="AA22" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="n">
+        <v>387</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>389</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG22" t="n">
         <v>17</v>
       </c>
-      <c r="AC22" t="s">
-        <v>313</v>
-      </c>
-      <c r="AD22"/>
-      <c r="AE22" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>67</v>
-      </c>
       <c r="AH22" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>69</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AI22"/>
       <c r="AJ22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK22"/>
+        <v>392</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>122</v>
+      </c>
       <c r="AL22" t="s">
-        <v>315</v>
+        <v>76</v>
       </c>
       <c r="AM22" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN22" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO22" t="s">
-        <v>316</v>
-      </c>
-      <c r="AP22" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP22"/>
       <c r="AQ22" t="s">
-        <v>174</v>
+        <v>393</v>
       </c>
       <c r="AR22" t="s">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AS22" t="s">
-        <v>178</v>
+        <v>383</v>
       </c>
       <c r="AT22" t="s">
-        <v>317</v>
-      </c>
-      <c r="AU22" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>384</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>211</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>394</v>
+      </c>
+      <c r="AY22" t="n">
         <v>0</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AZ22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E23" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="F23" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="G23" t="s">
-        <v>318</v>
+        <v>395</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="M23" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O23" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P23" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q23"/>
       <c r="R23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S23"/>
       <c r="T23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V23"/>
       <c r="W23"/>
       <c r="X23"/>
       <c r="Y23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z23" t="s">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AA23" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB23" t="n">
+        <v>398</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>390</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>378</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG23" t="n">
         <v>13</v>
       </c>
-      <c r="AC23" t="s">
-        <v>320</v>
-      </c>
-      <c r="AD23"/>
-      <c r="AE23" t="s">
-        <v>321</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>67</v>
-      </c>
       <c r="AH23" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>69</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AI23"/>
       <c r="AJ23" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK23"/>
+        <v>401</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>122</v>
+      </c>
       <c r="AL23" t="s">
-        <v>322</v>
+        <v>76</v>
       </c>
       <c r="AM23" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO23" t="s">
-        <v>323</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP23"/>
       <c r="AQ23" t="s">
-        <v>174</v>
+        <v>402</v>
       </c>
       <c r="AR23" t="s">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AS23" t="s">
-        <v>178</v>
+        <v>383</v>
       </c>
       <c r="AT23" t="s">
-        <v>324</v>
-      </c>
-      <c r="AU23" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>384</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>211</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>403</v>
+      </c>
+      <c r="AY23" t="n">
         <v>0</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AZ23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N24" t="s">
-        <v>325</v>
+        <v>404</v>
       </c>
       <c r="O24" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P24" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q24"/>
       <c r="R24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S24"/>
       <c r="T24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V24"/>
       <c r="W24"/>
       <c r="X24"/>
       <c r="Y24" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z24" t="s">
-        <v>62</v>
+        <v>405</v>
       </c>
       <c r="AA24" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB24" t="n">
+        <v>406</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>378</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG24" t="n">
         <v>17</v>
       </c>
-      <c r="AC24" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD24"/>
-      <c r="AE24" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>67</v>
-      </c>
       <c r="AH24" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>69</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AI24"/>
       <c r="AJ24" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK24"/>
+        <v>185</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>122</v>
+      </c>
       <c r="AL24" t="s">
-        <v>327</v>
+        <v>76</v>
       </c>
       <c r="AM24" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO24" t="s">
-        <v>328</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP24"/>
       <c r="AQ24" t="s">
-        <v>174</v>
+        <v>410</v>
       </c>
       <c r="AR24" t="s">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AS24" t="s">
-        <v>115</v>
+        <v>383</v>
       </c>
       <c r="AT24" t="s">
-        <v>330</v>
-      </c>
-      <c r="AU24" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>411</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>412</v>
+      </c>
+      <c r="AY24" t="n">
         <v>0</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AZ24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G25" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L25" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="O25" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P25" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q25"/>
       <c r="R25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S25"/>
       <c r="T25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V25"/>
       <c r="W25"/>
       <c r="X25"/>
       <c r="Y25" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="Z25" t="s">
-        <v>63</v>
+        <v>413</v>
       </c>
       <c r="AA25" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB25" t="n">
+        <v>414</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>417</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG25" t="n">
         <v>14</v>
       </c>
-      <c r="AC25" t="s">
-        <v>332</v>
-      </c>
-      <c r="AD25"/>
-      <c r="AE25" t="s">
-        <v>333</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>67</v>
-      </c>
       <c r="AH25" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>69</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="AI25"/>
       <c r="AJ25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK25"/>
+        <v>419</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>122</v>
+      </c>
       <c r="AL25" t="s">
-        <v>334</v>
+        <v>76</v>
       </c>
       <c r="AM25" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO25" t="s">
-        <v>335</v>
-      </c>
-      <c r="AP25" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP25"/>
       <c r="AQ25" t="s">
-        <v>174</v>
+        <v>420</v>
       </c>
       <c r="AR25" t="s">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AS25" t="s">
-        <v>115</v>
+        <v>383</v>
       </c>
       <c r="AT25" t="s">
-        <v>336</v>
-      </c>
-      <c r="AU25" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU25" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>411</v>
+      </c>
+      <c r="AW25" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>421</v>
+      </c>
+      <c r="AY25" t="n">
         <v>0</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AZ25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M26" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="N26" t="s">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="O26" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="Q26"/>
       <c r="R26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S26"/>
       <c r="T26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V26"/>
       <c r="W26"/>
       <c r="X26"/>
       <c r="Y26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z26" t="s">
-        <v>62</v>
+        <v>422</v>
       </c>
       <c r="AA26" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB26" t="n">
+        <v>423</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>268</v>
+      </c>
+      <c r="AG26" t="n">
         <v>18</v>
       </c>
-      <c r="AC26" t="s">
-        <v>337</v>
-      </c>
-      <c r="AD26"/>
-      <c r="AE26" t="s">
-        <v>338</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>67</v>
-      </c>
       <c r="AH26" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>69</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="AI26"/>
       <c r="AJ26" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK26"/>
+        <v>427</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>122</v>
+      </c>
       <c r="AL26" t="s">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="AM26" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AN26" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AO26" t="s">
-        <v>340</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>308</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AP26"/>
       <c r="AQ26" t="s">
-        <v>174</v>
+        <v>428</v>
       </c>
       <c r="AR26" t="s">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AS26" t="s">
-        <v>115</v>
+        <v>383</v>
       </c>
       <c r="AT26" t="s">
-        <v>341</v>
-      </c>
-      <c r="AU26" t="n">
+        <v>383</v>
+      </c>
+      <c r="AU26" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>411</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>429</v>
+      </c>
+      <c r="AY26" t="n">
         <v>0</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AZ26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4665,7 +5233,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -4689,19 +5257,19 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>342</v>
+        <v>430</v>
       </c>
       <c r="J1" t="s">
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="K1" t="s">
-        <v>344</v>
+        <v>432</v>
       </c>
       <c r="L1" t="s">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="M1" t="s">
-        <v>346</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
